--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125730768</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125730768</v>
       </c>
       <c r="B4" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125730768</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125730768</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125730768</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>134268440</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>134265426</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>134268490</v>
       </c>
       <c r="B7" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134268226</v>
+        <v>134265455</v>
       </c>
       <c r="B8" t="n">
-        <v>79978</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,21 +1296,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520899</v>
+        <v>520834</v>
       </c>
       <c r="R8" t="n">
-        <v>6848140</v>
+        <v>6848156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134265455</v>
+        <v>134268226</v>
       </c>
       <c r="B9" t="n">
-        <v>79025</v>
+        <v>79985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520834</v>
+        <v>520899</v>
       </c>
       <c r="R9" t="n">
-        <v>6848156</v>
+        <v>6848140</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>134265459</v>
       </c>
       <c r="B10" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>134265418</v>
       </c>
       <c r="B11" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>134268526</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>134268781</v>
       </c>
       <c r="B13" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>134268519</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>134268430</v>
       </c>
       <c r="B15" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>134268578</v>
       </c>
       <c r="B16" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>134273597</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117398743</v>
+        <v>134265455</v>
       </c>
       <c r="B2" t="n">
-        <v>78217</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521028</v>
+        <v>520834</v>
       </c>
       <c r="R2" t="n">
-        <v>6848094</v>
+        <v>6848156</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117398759</v>
+        <v>134268578</v>
       </c>
       <c r="B3" t="n">
-        <v>78216</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521028</v>
+        <v>521020</v>
       </c>
       <c r="R3" t="n">
-        <v>6848094</v>
+        <v>6848137</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,57 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125730768</v>
+        <v>134268519</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttkölsmyrorna, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520819</v>
+        <v>520973</v>
       </c>
       <c r="R4" t="n">
-        <v>6848169</v>
+        <v>6848123</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134268440</v>
+        <v>134268526</v>
       </c>
       <c r="B5" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520933</v>
+        <v>520973</v>
       </c>
       <c r="R5" t="n">
-        <v>6848133</v>
+        <v>6848122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,48 +1063,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134265426</v>
+        <v>134273597</v>
       </c>
       <c r="B6" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520837</v>
+        <v>521050</v>
       </c>
       <c r="R6" t="n">
-        <v>6848164</v>
+        <v>6848080</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,9 +1131,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,22 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134268490</v>
+        <v>117398759</v>
       </c>
       <c r="B7" t="n">
-        <v>79985</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,34 +1181,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520962</v>
+        <v>521028</v>
       </c>
       <c r="R7" t="n">
-        <v>6848127</v>
+        <v>6848094</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,12 +1239,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1273,22 +1264,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134265455</v>
+        <v>134265426</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520834</v>
+        <v>520837</v>
       </c>
       <c r="R8" t="n">
-        <v>6848156</v>
+        <v>6848164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134268226</v>
+        <v>134268440</v>
       </c>
       <c r="B9" t="n">
-        <v>79985</v>
+        <v>79130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520899</v>
+        <v>520933</v>
       </c>
       <c r="R9" t="n">
-        <v>6848140</v>
+        <v>6848133</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134265459</v>
+        <v>134265418</v>
       </c>
       <c r="B10" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1514,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520833</v>
+        <v>520839</v>
       </c>
       <c r="R10" t="n">
-        <v>6848157</v>
+        <v>6848162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134265418</v>
+        <v>134265459</v>
       </c>
       <c r="B11" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1611,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520839</v>
+        <v>520833</v>
       </c>
       <c r="R11" t="n">
-        <v>6848162</v>
+        <v>6848157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134268526</v>
+        <v>134268226</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520973</v>
+        <v>520899</v>
       </c>
       <c r="R12" t="n">
-        <v>6848122</v>
+        <v>6848140</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134268781</v>
+        <v>134268430</v>
       </c>
       <c r="B13" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1805,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521042</v>
+        <v>520934</v>
       </c>
       <c r="R13" t="n">
-        <v>6848160</v>
+        <v>6848132</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134268519</v>
+        <v>134268490</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1869,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520973</v>
+        <v>520962</v>
       </c>
       <c r="R14" t="n">
-        <v>6848123</v>
+        <v>6848127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134268430</v>
+        <v>134268781</v>
       </c>
       <c r="B15" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1999,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520934</v>
+        <v>521042</v>
       </c>
       <c r="R15" t="n">
-        <v>6848132</v>
+        <v>6848160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,48 +2052,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134268578</v>
+        <v>134273593</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>103907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>223284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521020</v>
+        <v>521057</v>
       </c>
       <c r="R16" t="n">
-        <v>6848137</v>
+        <v>6848024</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2129,9 +2120,24 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre sälg med tickor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2146,22 +2152,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134273597</v>
+        <v>117398743</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,37 +2175,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521050</v>
+        <v>521028</v>
       </c>
       <c r="R17" t="n">
-        <v>6848080</v>
+        <v>6848094</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2223,22 +2233,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2253,15 +2258,112 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125730768</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyrorna, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>520819</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6848169</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18103-2024 artfynd.xlsx
+++ b/artfynd/A 18103-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134265455</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268578</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268526</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273597</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398759</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134265426</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268440</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134265418</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134265459</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268226</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1855,6 +1915,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268430</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268490</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134268781</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2161,6 +2236,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273593</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2267,6 +2347,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398743</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,8 +2449,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125730768</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>